--- a/ExcelFile/2025-10-13/CityBlackList/Download/CityBlackList_20251013.xlsx
+++ b/ExcelFile/2025-10-13/CityBlackList/Download/CityBlackList_20251013.xlsx
@@ -102,7 +102,7 @@
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>3</v>
